--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1939,20 +1939,14 @@
           <t>OA5YizjL</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="B95" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C95" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="96">
@@ -1961,19 +1955,255 @@
           <t>lEQmcVR0</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
+      <c r="B96" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C96" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>2yXIHV57</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>GM5aU8kD</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>r97iWUK0</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>MaSQpUZg</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>WUmnhCsK</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>nsErYjjl</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>UsP4uZcE</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>4rrRVcF7</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>3.25</t>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2.10</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,20 +2227,14 @@
           <t>hhlQ5IbD</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="B113" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C113" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D113" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="114">
@@ -2249,19 +2243,189 @@
           <t>0pvInj5s</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
+      <c r="B114" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C114" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>WlzDg17E</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>IoCT4kRP</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>zyWS0tQi</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>5.00</t>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>06FhaTlm</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>UPVYr846</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>8WI0c7Ja</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>QiPssnZI</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2.15</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2259,20 +2259,14 @@
           <t>vmgpBDzg</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B115" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="116">
@@ -2281,20 +2275,14 @@
           <t>WlzDg17E</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B116" t="n">
+        <v>2</v>
+      </c>
+      <c r="C116" t="n">
+        <v>3</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="117">
@@ -2303,20 +2291,14 @@
           <t>IoCT4kRP</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B117" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C117" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D117" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="118">
@@ -2325,20 +2307,14 @@
           <t>zyWS0tQi</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B118" t="n">
+        <v>3</v>
+      </c>
+      <c r="C118" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="119">
@@ -2347,20 +2323,14 @@
           <t>06FhaTlm</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B119" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C119" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="120">
@@ -2369,20 +2339,14 @@
           <t>UPVYr846</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B120" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C120" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -2391,20 +2355,14 @@
           <t>8WI0c7Ja</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C121" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="122">
@@ -2413,19 +2371,101 @@
           <t>QiPssnZI</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2.15</t>
+      <c r="B122" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>zoZtwwYp</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>8lUzaKf4</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>5.75</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2387,20 +2387,14 @@
           <t>6FCg7VZH</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B123" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="124">
@@ -2409,20 +2403,14 @@
           <t>bk9o9i55</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B124" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C124" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="125">
@@ -2431,20 +2419,14 @@
           <t>zoZtwwYp</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B125" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C125" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="126">
@@ -2453,19 +2435,145 @@
           <t>8lUzaKf4</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>5.75</t>
+      <c r="B126" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C126" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D126" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2.20</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2547,20 +2547,14 @@
           <t>CGH7Enso</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B133" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="134">
@@ -2569,20 +2563,14 @@
           <t>0dMqm7mA</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B134" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D134" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="135">
@@ -2591,20 +2579,14 @@
           <t>vsYzkTIc</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="B135" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="136">
@@ -2613,20 +2595,14 @@
           <t>CtRiexfT</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B136" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="137">
@@ -2635,20 +2611,14 @@
           <t>WjsR9y9M</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B137" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="138">
@@ -2657,20 +2627,14 @@
           <t>SGTLiuxR</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D138" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="139">
@@ -2679,20 +2643,14 @@
           <t>jyOc4FWq</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B139" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="140">
@@ -2701,20 +2659,14 @@
           <t>xU3hQdg3</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B140" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C140" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="141">
@@ -2723,20 +2675,14 @@
           <t>dYQ52g1d</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B141" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D141" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="142">
@@ -2745,20 +2691,14 @@
           <t>bwqJBcvA</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B142" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C142" t="n">
+        <v>3</v>
+      </c>
+      <c r="D142" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="143">
@@ -2767,19 +2707,167 @@
           <t>2BkADJ9c</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C143" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2.00</t>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>hCffxjZi</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>8MPiooIM</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>4GNqcbPG</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2.45</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2547,20 +2547,14 @@
           <t>CGH7Enso</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B133" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="134">
@@ -2569,20 +2563,14 @@
           <t>0dMqm7mA</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B134" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D134" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="135">
@@ -2591,20 +2579,14 @@
           <t>vsYzkTIc</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="B135" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="136">
@@ -2613,20 +2595,14 @@
           <t>CtRiexfT</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B136" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="137">
@@ -2635,20 +2611,14 @@
           <t>WjsR9y9M</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B137" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="138">
@@ -2657,20 +2627,14 @@
           <t>SGTLiuxR</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D138" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="139">
@@ -2679,20 +2643,14 @@
           <t>jyOc4FWq</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B139" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="140">
@@ -2701,20 +2659,14 @@
           <t>xU3hQdg3</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B140" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C140" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="141">
@@ -2723,20 +2675,14 @@
           <t>dYQ52g1d</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B141" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D141" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="142">
@@ -2745,20 +2691,14 @@
           <t>bwqJBcvA</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B142" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C142" t="n">
+        <v>3</v>
+      </c>
+      <c r="D142" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="143">
@@ -2767,19 +2707,563 @@
           <t>2BkADJ9c</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C143" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>hCffxjZi</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>8MPiooIM</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>WQczyE7L</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>d8sFTVae</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>tM09MEhS</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>ULuNR9U7</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2.00</t>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>r5HuFWp2</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>xhnuHhGk</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>pf70OzOF</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>AB9Rxzw9</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>OnFinJal</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>4GNqcbPG</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2.45</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D168"/>
+  <dimension ref="A1:D177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2723,20 +2723,14 @@
           <t>S66OuPup</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="B144" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C144" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="145">
@@ -2745,20 +2739,14 @@
           <t>6HPisxHl</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B145" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D145" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="146">
@@ -2767,20 +2755,14 @@
           <t>nTCJapXF</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B146" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="147">
@@ -2789,20 +2771,14 @@
           <t>EsTauGo1</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B147" t="n">
+        <v>2</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="148">
@@ -2811,20 +2787,14 @@
           <t>6V4QeyWs</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B148" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C148" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D148" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="149">
@@ -2833,20 +2803,14 @@
           <t>v39B1623</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="B149" t="n">
+        <v>7</v>
+      </c>
+      <c r="C149" t="n">
+        <v>5</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="150">
@@ -2855,20 +2819,14 @@
           <t>noOg1c8K</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B150" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="151">
@@ -2877,20 +2835,14 @@
           <t>fiy8wfGD</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B151" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C151" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D151" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="152">
@@ -2899,20 +2851,14 @@
           <t>0K4Ww3Ad</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B152" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C152" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D152" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="153">
@@ -2921,20 +2867,14 @@
           <t>Qw81zU34</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B153" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D153" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="154">
@@ -2943,20 +2883,14 @@
           <t>M51AY7YG</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B154" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="155">
@@ -2965,20 +2899,14 @@
           <t>E3tkRPQj</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B155" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C155" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D155" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="156">
@@ -2987,20 +2915,14 @@
           <t>fJaIWo3T</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B156" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C156" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D156" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="157">
@@ -3009,20 +2931,14 @@
           <t>hCffxjZi</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B157" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C157" t="n">
+        <v>5</v>
+      </c>
+      <c r="D157" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="158">
@@ -3031,20 +2947,14 @@
           <t>8MPiooIM</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="B158" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C158" t="n">
+        <v>6</v>
+      </c>
+      <c r="D158" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="159">
@@ -3053,20 +2963,14 @@
           <t>WQczyE7L</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B159" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C159" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="160">
@@ -3075,20 +2979,14 @@
           <t>d8sFTVae</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B160" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D160" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -3097,20 +2995,14 @@
           <t>tM09MEhS</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="B161" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D161" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="162">
@@ -3119,20 +3011,14 @@
           <t>ULuNR9U7</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B162" t="n">
+        <v>2</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="163">
@@ -3141,20 +3027,14 @@
           <t>r5HuFWp2</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B163" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C163" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="164">
@@ -3163,20 +3043,14 @@
           <t>xhnuHhGk</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B164" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D164" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="165">
@@ -3185,20 +3059,14 @@
           <t>pf70OzOF</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="B165" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="166">
@@ -3207,20 +3075,14 @@
           <t>AB9Rxzw9</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B166" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C166" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="167">
@@ -3229,20 +3091,14 @@
           <t>OnFinJal</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B167" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="168">
@@ -3251,19 +3107,211 @@
           <t>4GNqcbPG</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B168" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C168" t="n">
+        <v>3</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>Aw6Go4Lt</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
         <is>
           <t>2.80</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2.45</t>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>rkVhpcU0</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>pUN9kDME</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>bDHWsMK5</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>65aPqrjg</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>CrvjVry0</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>baxbTM5C</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>fRV6R0zP</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>KS5ut0kI</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>3.25</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D177"/>
+  <dimension ref="A1:D190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3123,20 +3123,14 @@
           <t>Aw6Go4Lt</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B169" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C169" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D169" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="170">
@@ -3145,20 +3139,14 @@
           <t>rkVhpcU0</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B170" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D170" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="171">
@@ -3167,20 +3155,14 @@
           <t>pUN9kDME</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B171" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="172">
@@ -3189,20 +3171,14 @@
           <t>bDHWsMK5</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B172" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D172" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="173">
@@ -3211,20 +3187,14 @@
           <t>65aPqrjg</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B173" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C173" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="174">
@@ -3233,20 +3203,14 @@
           <t>CrvjVry0</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="B174" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C174" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D174" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="175">
@@ -3255,20 +3219,14 @@
           <t>baxbTM5C</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B175" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D175" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="176">
@@ -3277,20 +3235,14 @@
           <t>fRV6R0zP</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B176" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="177">
@@ -3299,19 +3251,299 @@
           <t>KS5ut0kI</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
+      <c r="B177" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D177" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>jFY0ryaD</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>8SrDxn0N</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>8nRerjWo</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>t0P3tU0b</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>Sh9mvvKU</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
         <is>
           <t>3.25</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>3.25</t>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>h0KqXPNp</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>K6CVfTFi</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>02u5v8VA</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2.35</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D190"/>
+  <dimension ref="A1:D194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,20 +3267,14 @@
           <t>lxyu7Met</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
+      <c r="B178" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C178" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D178" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="179">
@@ -3289,20 +3283,14 @@
           <t>xb7MlutC</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B179" t="n">
+        <v>4</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="180">
@@ -3311,20 +3299,14 @@
           <t>v3PZcqJP</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B180" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D180" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="181">
@@ -3333,20 +3315,14 @@
           <t>zBdshgV6</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B181" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C181" t="n">
+        <v>5</v>
+      </c>
+      <c r="D181" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="182">
@@ -3355,20 +3331,14 @@
           <t>MRfkjXaJ</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B182" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C182" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="183">
@@ -3377,20 +3347,14 @@
           <t>jFY0ryaD</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="B183" t="n">
+        <v>4</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="184">
@@ -3399,20 +3363,14 @@
           <t>8SrDxn0N</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B184" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="185">
@@ -3421,20 +3379,14 @@
           <t>8nRerjWo</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B185" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C185" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="186">
@@ -3443,20 +3395,14 @@
           <t>t0P3tU0b</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B186" t="n">
+        <v>2</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D186" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="187">
@@ -3465,20 +3411,14 @@
           <t>Sh9mvvKU</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B187" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C187" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="188">
@@ -3487,20 +3427,14 @@
           <t>h0KqXPNp</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B188" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C188" t="n">
+        <v>3</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="189">
@@ -3509,20 +3443,14 @@
           <t>K6CVfTFi</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B189" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C189" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D189" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="190">
@@ -3531,19 +3459,101 @@
           <t>02u5v8VA</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B190" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D190" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>2.35</t>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2.80</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D205"/>
+  <dimension ref="A1:D212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3555,20 +3555,14 @@
           <t>Wf14adfU</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B196" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D196" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="197">
@@ -3577,20 +3571,14 @@
           <t>z9REJaun</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="B197" t="n">
+        <v>3</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="198">
@@ -3599,20 +3587,14 @@
           <t>xYNVFHvB</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
+      <c r="B198" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C198" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D198" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="199">
@@ -3621,20 +3603,14 @@
           <t>jXmAqfD7</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B199" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C199" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="200">
@@ -3643,20 +3619,14 @@
           <t>ETmRq37j</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B200" t="n">
+        <v>3</v>
+      </c>
+      <c r="C200" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="201">
@@ -3665,20 +3635,14 @@
           <t>rocekPqT</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B201" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="202">
@@ -3687,20 +3651,14 @@
           <t>GAud7c5E</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B202" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D202" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="203">
@@ -3709,20 +3667,14 @@
           <t>WABm6viK</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B203" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="204">
@@ -3731,20 +3683,14 @@
           <t>xQT45yzR</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B204" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D204" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="205">
@@ -3753,19 +3699,167 @@
           <t>MidgmxEr</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2.80</t>
+      <c r="B205" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D205" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>fPQD76ac</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>5.00</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D212"/>
+  <dimension ref="A1:D222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3715,20 +3715,14 @@
           <t>OUcd1IPH</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
+      <c r="B206" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C206" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="207">
@@ -3737,20 +3731,14 @@
           <t>rZUMHwAb</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B207" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D207" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="208">
@@ -3759,20 +3747,14 @@
           <t>WhWcJjo3</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B208" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C208" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D208" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="209">
@@ -3781,20 +3763,14 @@
           <t>4nvCemgd</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B209" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D209" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="210">
@@ -3803,20 +3779,14 @@
           <t>IHSe3ve5</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B210" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C210" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D210" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="211">
@@ -3825,20 +3795,14 @@
           <t>8Kp3c9Oq</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B211" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C211" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="212">
@@ -3847,19 +3811,233 @@
           <t>fPQD76ac</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
+      <c r="B212" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D212" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>OAZJOoNr</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>WzwSMPie</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>5.00</t>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>xlCidXdD</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>lbfDWDYP</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>d47R8AtJ</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>4zEqbgS0</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>8UeBChsf</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>88Kz0Fcl</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>nF72EECs</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2.70</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D222"/>
+  <dimension ref="A1:D230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3827,20 +3827,14 @@
           <t>OAZJOoNr</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="B213" t="n">
+        <v>6</v>
+      </c>
+      <c r="C213" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="214">
@@ -3849,20 +3843,14 @@
           <t>WzwSMPie</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="B214" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C214" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D214" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="215">
@@ -3871,20 +3859,14 @@
           <t>vwbmU7aL</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B215" t="n">
+        <v>2</v>
+      </c>
+      <c r="C215" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D215" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="216">
@@ -3893,20 +3875,14 @@
           <t>xlCidXdD</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B216" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C216" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D216" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="217">
@@ -3915,20 +3891,14 @@
           <t>lbfDWDYP</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B217" t="n">
+        <v>2</v>
+      </c>
+      <c r="C217" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D217" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="218">
@@ -3937,20 +3907,14 @@
           <t>d47R8AtJ</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B218" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C218" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="219">
@@ -3959,20 +3923,14 @@
           <t>4zEqbgS0</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B219" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C219" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D219" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="220">
@@ -3981,20 +3939,14 @@
           <t>8UeBChsf</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B220" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D220" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="221">
@@ -4003,20 +3955,14 @@
           <t>88Kz0Fcl</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
+      <c r="B221" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="222">
@@ -4025,19 +3971,147 @@
           <t>nF72EECs</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>2.70</t>
+      <c r="B222" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D222" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C223" t="n">
+        <v>4</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C224" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D224" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C225" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D225" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C226" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D226" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>b9aoAn8k</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C227" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>S2WzL3M7</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C228" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D228" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>GWGWJzkK</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C229" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D229" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>2g2J0IEs</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>1.72</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D230"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4099,19 +4099,35 @@
           <t>2g2J0IEs</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>1.72</t>
+      <c r="B230" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C230" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>f5f1oGre</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>3.70</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4115,19 +4115,331 @@
           <t>f5f1oGre</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
+      <c r="B231" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C231" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D231" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C232" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D232" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C233" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D233" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C234" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D234" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>lYpTkOLs</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C235" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D235" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>Wplzx9A5</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C236" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D236" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>dheSbdqf</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D237" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>25dJuiBt</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C238" t="n">
+        <v>4</v>
+      </c>
+      <c r="D238" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>dW3GHvPj</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C239" t="n">
+        <v>3</v>
+      </c>
+      <c r="D239" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>OvR8LmQO</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C240" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D240" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>xrirzmuI</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>8rypRidm</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C242" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D242" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>zJfRwVug</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>xOS0N9eC</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
         <is>
           <t>3.70</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>5.75</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D249"/>
+  <dimension ref="A1:D258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4339,20 +4339,14 @@
           <t>AsQgyP6l</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
+      <c r="B245" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="246">
@@ -4361,20 +4355,14 @@
           <t>vNHAXt6D</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B246" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="247">
@@ -4383,20 +4371,14 @@
           <t>KdJMr7EE</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B247" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="248">
@@ -4405,20 +4387,14 @@
           <t>h2acepbK</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B248" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C248" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D248" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="249">
@@ -4427,19 +4403,211 @@
           <t>WdE2Z2y1</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
+      <c r="B249" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C249" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D249" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>K4kBwMoA</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>hImJy0GM</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>UD9kUH8d</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>Mm6sWwvp</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
         <is>
           <t>5.25</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>5.75</t>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>CYrglw0S</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>A9nxhL03</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>Oxd2urHc</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>IZkpjaVF</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>U5gzczE6</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2.55</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D258"/>
+  <dimension ref="A1:D276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4419,20 +4419,14 @@
           <t>K4kBwMoA</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B250" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C250" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D250" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="251">
@@ -4441,20 +4435,14 @@
           <t>hImJy0GM</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B251" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D251" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="252">
@@ -4463,20 +4451,14 @@
           <t>UD9kUH8d</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B252" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D252" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="253">
@@ -4485,20 +4467,14 @@
           <t>Mm6sWwvp</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B253" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D253" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="254">
@@ -4507,20 +4483,14 @@
           <t>CYrglw0S</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B254" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3</v>
+      </c>
+      <c r="D254" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="255">
@@ -4529,20 +4499,14 @@
           <t>A9nxhL03</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B255" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C255" t="n">
+        <v>5</v>
+      </c>
+      <c r="D255" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="256">
@@ -4551,20 +4515,14 @@
           <t>Oxd2urHc</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
+      <c r="B256" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D256" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="257">
@@ -4573,20 +4531,14 @@
           <t>IZkpjaVF</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B257" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D257" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="258">
@@ -4595,19 +4547,307 @@
           <t>U5gzczE6</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>2.55</t>
+      <c r="B258" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D258" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D259" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D260" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D261" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D262" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D263" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>3</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D264" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C265" t="n">
+        <v>5</v>
+      </c>
+      <c r="D265" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C267" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D267" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>W6sFgYy8</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D268" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2RkbcGxq</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D269" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>lrCa1peE</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C270" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D270" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>hh4S2xFL</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D271" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>tjU6aOPQ</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C272" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D272" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>QN5wf2ml</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C273" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D273" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>bgq7ef7e</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C274" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D274" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>QXnqeErJ</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C275" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D275" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>4WNXteh2</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>
